--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.81489537707138</v>
+        <v>4.0324204987741</v>
       </c>
       <c r="D2" t="n">
-        <v>24.84091282780232</v>
+        <v>4.036648334517877</v>
       </c>
       <c r="E2" t="n">
-        <v>22.25677205083078</v>
+        <v>3.616725458260002</v>
       </c>
       <c r="F2" t="n">
-        <v>21.50351571960118</v>
+        <v>3.494321304435191</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.48981995287062</v>
+        <v>6.417095742341476</v>
       </c>
       <c r="D3" t="n">
-        <v>38.87744510111884</v>
+        <v>6.317584828931811</v>
       </c>
       <c r="E3" t="n">
-        <v>22.25677205083078</v>
+        <v>3.616725458260002</v>
       </c>
       <c r="F3" t="n">
-        <v>21.50351571960118</v>
+        <v>3.494321304435191</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>77.62347488318814</v>
+        <v>12.61381466851807</v>
       </c>
       <c r="D4" t="n">
-        <v>75.82549753526219</v>
+        <v>12.32164334948011</v>
       </c>
       <c r="E4" t="n">
-        <v>22.25677205083078</v>
+        <v>3.616725458260002</v>
       </c>
       <c r="F4" t="n">
-        <v>21.50351571960118</v>
+        <v>3.494321304435191</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
